--- a/output/pdf_financials_xlsx/EPL.xlsx
+++ b/output/pdf_financials_xlsx/EPL.xlsx
@@ -7497,37 +7497,37 @@
         <v>0.615991</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.116405</v>
+        <v>-0.047799</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>1.199224</v>
+        <v>0.8863839999999999</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.242245</v>
+        <v>0.06671000000000001</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.014298</v>
+        <v>-0.54857</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.322379</v>
+        <v>-0.361149</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.5771230000000001</v>
+        <v>0.420407</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.819031</v>
+        <v>0.003472</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.245052</v>
+        <v>-1.118422</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.657985</v>
+        <v>-1.403582</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0.119995</v>
+        <v>0.08201700000000001</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0.038709</v>
+        <v>-0.022014</v>
       </c>
     </row>
     <row r="119">
@@ -22935,7 +22935,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/EPL.xlsx
+++ b/output/pdf_financials_xlsx/EPL.xlsx
@@ -1071,13 +1071,13 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.292945</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.386526</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.176608</v>
       </c>
     </row>
     <row r="13">
@@ -2039,13 +2039,13 @@
         <v>-0.568457</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>6.658894</v>
+        <v>6.365949</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.492727</v>
+        <v>-0.879253</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>2.01486</v>
+        <v>1.838252</v>
       </c>
     </row>
     <row r="28">
@@ -2155,13 +2155,13 @@
         <v>-0.360021</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>6.880262</v>
+        <v>6.587317</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.287182</v>
+        <v>-0.673708</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>2.200724</v>
+        <v>2.024116</v>
       </c>
     </row>
     <row r="30">
@@ -7867,13 +7867,13 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.027607</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.025138</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009391</v>
       </c>
       <c r="Q124" s="3" t="n">
         <v>0</v>
@@ -7925,13 +7925,13 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.027607</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.025138</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009391</v>
       </c>
       <c r="Q125" s="3" t="n">
         <v>0</v>
@@ -10018,7 +10018,11 @@
           <t>Reclamation deposits (Note 12) 55,956</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -11436,7 +11440,11 @@
           <t>Reclamation deposits (Note 11)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -12594,7 +12602,11 @@
           <t>Reclamation deposits (Note 12)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -24537,7 +24549,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -28148,7 +28164,11 @@
           <t>Increase (decrease) in reclamation deposits</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -45201,7 +45221,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -46902,7 +46922,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">

--- a/output/pdf_financials_xlsx/EPL.xlsx
+++ b/output/pdf_financials_xlsx/EPL.xlsx
@@ -7146,34 +7146,34 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.023376</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.001619</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.005238</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.033714</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.0224</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.004432</v>
       </c>
       <c r="Q112" s="3" t="n">
         <v>0</v>
@@ -25885,7 +25885,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/EPL.xlsx
+++ b/output/pdf_financials_xlsx/EPL.xlsx
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-4.522537</v>
+        <v>-2.586277</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-6.289658</v>
+        <v>-5.65954</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-1.449642</v>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.93626</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.630118</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.38118</v>
+        <v>-0.38118</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0.274968</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.522537</v>
+        <v>-2.586277</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.289658</v>
+        <v>-5.65954</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.449642</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.522537</v>
+        <v>-2.586277</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.289658</v>
+        <v>-5.65954</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.068055</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-200.4709754977491</v>
+        <v>-114.6421738721855</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-370.4359543838385</v>
+        <v>-333.3244989272086</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-43.60865938450445</v>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-74.86669061357311</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-11.13373171671196</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-26.29476794960411</v>
@@ -7305,55 +7305,55 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.01749</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.60241</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>1.712211</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>1.973417</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.452552</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.422423</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.061867</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.093488</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.515968</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.716804</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.540358</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.088855</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.182008</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>3.485022</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.378723</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.385905</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.153569</v>
       </c>
     </row>
     <row r="116">
@@ -22504,7 +22504,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -38457,7 +38461,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -41833,7 +41841,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E340" s="5" t="n">
         <v>0.01749</v>
       </c>
@@ -58948,7 +58960,11 @@
           <t>Deferred income tax recovery (Note 14 )</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
@@ -61572,7 +61588,11 @@
           <t>Future income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
           <t>-</t>
@@ -62871,7 +62891,11 @@
           <t>Future income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E554" s="5" t="n">
         <v>1.93626</v>
       </c>
